--- a/src/main/resources/excel/imagen.xlsx
+++ b/src/main/resources/excel/imagen.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1 Images" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="9">
   <si>
     <t xml:space="preserve">a</t>
   </si>
@@ -133,7 +133,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -160,9 +160,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>50760</xdr:colOff>
+      <xdr:colOff>50400</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>5746680</xdr:rowOff>
+      <xdr:rowOff>5746320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -176,7 +176,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6502320" y="0"/>
-          <a:ext cx="8178840" cy="5746680"/>
+          <a:ext cx="8178480" cy="5746320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -198,9 +198,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>742680</xdr:colOff>
+      <xdr:colOff>742320</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>3657240</xdr:rowOff>
+      <xdr:rowOff>3656880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -214,7 +214,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6502320" y="6378120"/>
-          <a:ext cx="3993840" cy="3657240"/>
+          <a:ext cx="3993480" cy="3656880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -241,9 +241,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>94680</xdr:colOff>
+      <xdr:colOff>94320</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>3612960</xdr:rowOff>
+      <xdr:rowOff>3612600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -257,7 +257,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6502320" y="0"/>
-          <a:ext cx="5784480" cy="3612960"/>
+          <a:ext cx="5784120" cy="3612600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -279,9 +279,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>786960</xdr:colOff>
+      <xdr:colOff>786600</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>2393640</xdr:rowOff>
+      <xdr:rowOff>2393280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -295,7 +295,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6502320" y="4467960"/>
-          <a:ext cx="3225600" cy="2393640"/>
+          <a:ext cx="3225240" cy="2393280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -422,7 +422,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
@@ -531,6 +531,342 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -551,7 +887,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
@@ -660,6 +996,300 @@
         <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>2</v>
       </c>
     </row>
